--- a/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
+++ b/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
@@ -4769,7 +4769,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -5509,11 +5509,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-11 15:18</t>
+          <t>2026-10-11 15:21</t>
         </is>
       </c>
       <c r="D95" t="n">

--- a/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
+++ b/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
@@ -3798,7 +3798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3830,13 +3830,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>161.8</v>
+        <v>34.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3846,17 +3846,20 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>286.8</v>
+        <v>59</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2022/7269438</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3868,17 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2024/8409918</t>
         </is>
       </c>
     </row>
@@ -3884,17 +3887,14 @@
         <v>2023</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>70</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.8</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2024/8409918</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8577177</t>
         </is>
       </c>
     </row>
@@ -3903,30 +3903,33 @@
         <v>2023</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8577177</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8701793</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>87</v>
+        <v>99</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8701793</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
         </is>
       </c>
     </row>
@@ -3935,17 +3938,17 @@
         <v>2024</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2025/9100543</t>
         </is>
       </c>
     </row>
@@ -3954,17 +3957,17 @@
         <v>2024</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2025/9100543</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
         </is>
       </c>
     </row>
@@ -3973,36 +3976,36 @@
         <v>2024</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D10" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>5.5</v>
+        <v>1.19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
         </is>
       </c>
     </row>
@@ -4011,17 +4014,17 @@
         <v>2025</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>1.19</v>
+        <v>2.29</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2026/9761841</t>
         </is>
       </c>
     </row>
@@ -4030,17 +4033,17 @@
         <v>2025</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>2.29</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2026/9761841</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
         </is>
       </c>
     </row>
@@ -4049,36 +4052,36 @@
         <v>2025</v>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6</v>
+        <v>0.96</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
         </is>
       </c>
     </row>
@@ -4087,34 +4090,15 @@
         <v>2026</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D16" t="n">
-        <v>0.96</v>
+        <v>2.13</v>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B17" t="n">
-        <v>6</v>
-      </c>
-      <c r="C17" t="n">
-        <v>87</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2026/9761841</t>
         </is>
@@ -4769,7 +4753,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -4789,7 +4773,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4809,7 +4793,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -4829,7 +4813,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -4849,7 +4833,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -4869,7 +4853,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4889,7 +4873,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -4909,7 +4893,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -4929,7 +4913,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4949,7 +4933,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -4969,7 +4953,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -4989,7 +4973,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5009,7 +4993,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -5029,7 +5013,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -5049,7 +5033,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5069,7 +5053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -5089,7 +5073,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -5109,7 +5093,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5129,7 +5113,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5149,7 +5133,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -5169,7 +5153,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -5189,7 +5173,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -5209,7 +5193,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -5229,7 +5213,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -5249,7 +5233,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -5269,7 +5253,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -5289,7 +5273,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -5309,7 +5293,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -5329,7 +5313,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -5349,7 +5333,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -5369,7 +5353,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -5389,7 +5373,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -5409,7 +5393,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -5429,7 +5413,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -5449,7 +5433,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -5469,7 +5453,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -5489,7 +5473,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -5509,7 +5493,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -5529,7 +5513,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -5549,7 +5533,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -5569,7 +5553,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -5589,7 +5573,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -5609,7 +5593,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -5629,7 +5613,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -5649,7 +5633,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -5669,7 +5653,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -5689,7 +5673,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -5709,7 +5693,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -5729,7 +5713,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -5749,7 +5733,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -5769,7 +5753,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -5789,7 +5773,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -5809,7 +5793,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -5829,7 +5813,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -5849,7 +5833,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -5869,7 +5853,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -5889,7 +5873,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -5909,7 +5893,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -5929,7 +5913,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -5949,7 +5933,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -5969,7 +5953,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -5989,7 +5973,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -6009,7 +5993,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -6029,7 +6013,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-11 15:21</t>
+          <t>2026-10-11 15:24</t>
         </is>
       </c>
       <c r="D95" t="n">

--- a/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
+++ b/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chart - Leviathan by destinatio" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Chart - Exports" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Quarterly" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Leviathan" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Tamar" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Karish YTD" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Reports" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Leviathan by destinatio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Exports" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leviathan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tamar" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Karish YTD" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,8 +26,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -67,12 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -150,13 +151,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -182,22 +183,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$27</f>
+              <f>'Chart'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$27</f>
+              <f>'Chart'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -210,22 +211,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$27</f>
+              <f>'Chart'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$27</f>
+              <f>'Chart'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -238,22 +239,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$27</f>
+              <f>'Chart'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$27</f>
+              <f>'Chart'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -274,8 +275,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -287,8 +288,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-        <tickMarkSkip val="2"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -301,8 +302,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -319,7 +320,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -333,7 +334,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -342,13 +343,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -374,10 +375,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -402,10 +403,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -430,10 +431,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -466,8 +467,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -493,8 +494,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -511,7 +512,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -525,7 +526,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -534,13 +535,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -566,10 +567,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -594,10 +595,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -622,10 +623,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -658,8 +659,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -685,8 +686,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -703,7 +704,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -717,7 +718,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -726,7 +727,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -741,9 +742,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -753,7 +754,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -768,9 +769,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -780,7 +781,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -795,9 +796,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1122,7 +1123,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1137,7 +1137,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1152,7 +1151,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1167,7 +1165,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -1193,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1222,276 +1219,142 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>43831</v>
+      <c r="A2" s="5" t="n">
+        <v>45292</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6209178021978023</v>
+        <v>1.008991428571429</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.024514373626374</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4656883516483517</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>43922</v>
+      <c r="A3" s="5" t="n">
+        <v>45383</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5821104395604396</v>
+        <v>1.086606153846154</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8770463956043956</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5044957142857144</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>44013</v>
+      <c r="A4" s="5" t="n">
+        <v>45474</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8828675</v>
+        <v>1.189951847826087</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.044086782608696</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6525542391304348</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>44105</v>
+      <c r="A5" s="5" t="n">
+        <v>45566</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7293253260869565</v>
+        <v>1.036409673913044</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9481229239130435</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4990120652173914</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>44197</v>
+      <c r="A6" s="5" t="n">
+        <v>45658</v>
       </c>
       <c r="B6" t="n">
-        <v>1.059441</v>
+        <v>1.137918111111111</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.0241263</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4669388111111111</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>44287</v>
+      <c r="A7" s="5" t="n">
+        <v>45748</v>
       </c>
       <c r="B7" t="n">
-        <v>1.086606153846154</v>
+        <v>0.7761472527472528</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.005110692307692</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4268809890109891</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>44378</v>
+      <c r="A8" s="5" t="n">
+        <v>45839</v>
       </c>
       <c r="B8" t="n">
+        <v>1.189951847826087</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.036409673913044</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6563927934782608</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B9" t="n">
         <v>1.074795217391304</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.9212530434782609</v>
+      <c r="C9" t="n">
+        <v>0.8252891847826086</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.614168695652174</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>44562</v>
+      <c r="A10" s="5" t="n">
+        <v>46023</v>
       </c>
       <c r="B10" t="n">
-        <v>1.059441</v>
+        <v>0.7455325555555556</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.082984133333333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3766901333333333</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>44652</v>
+      <c r="A11" s="5" t="n">
+        <v>46113</v>
       </c>
       <c r="B11" t="n">
-        <v>1.086606153846154</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1.151566304347826</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1.113180760869565</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1.098679555555556</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.2746698888888889</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.970184065934066</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.4268809890109891</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1.113180760869565</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1.074795217391304</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1.008991428571429</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.024514373626374</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.4656883516483517</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1.086606153846154</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.8770463956043956</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.5044957142857144</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B20" t="n">
-        <v>1.189951847826087</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.044086782608696</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.6525542391304348</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1.036409673913044</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.9481229239130435</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.4990120652173914</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B22" t="n">
-        <v>1.137918111111111</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.0241263</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.4669388111111111</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.7761472527472528</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.005110692307692</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.4268809890109891</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B24" t="n">
-        <v>1.189951847826087</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.036409673913044</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.6563927934782608</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B25" t="n">
-        <v>1.074795217391304</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.8252891847826086</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.614168695652174</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.7455325555555556</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.082984133333333</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.3766901333333333</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B27" t="n">
         <v>1.047798791208791</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C11" t="n">
         <v>1.051679527472527</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D11" t="n">
         <v>0.4540461428571428</v>
       </c>
     </row>
@@ -1536,7 +1399,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B2" t="n">
@@ -1550,7 +1413,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B3" t="n">
@@ -1564,7 +1427,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B4" t="n">
@@ -1578,7 +1441,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B5" t="n">
@@ -1592,7 +1455,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B6" t="n">
@@ -1606,7 +1469,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B7" t="n">
@@ -1620,7 +1483,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1634,7 +1497,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -1648,7 +1511,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B10" t="n">
@@ -1662,7 +1525,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B11" t="n">
@@ -1676,7 +1539,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B12" t="n">
@@ -1690,7 +1553,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B13" t="n">
@@ -1704,7 +1567,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B14" t="n">
@@ -1718,7 +1581,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B15" t="n">
@@ -1732,7 +1595,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B16" t="n">
@@ -1746,7 +1609,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B17" t="n">
@@ -1760,7 +1623,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B18" t="n">
@@ -1774,7 +1637,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B19" t="n">
@@ -1788,7 +1651,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B20" t="n">
@@ -1802,7 +1665,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B21" t="n">
@@ -1816,7 +1679,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B22" t="n">
@@ -1830,7 +1693,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B23" t="n">
@@ -1844,7 +1707,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B24" t="n">
@@ -1858,7 +1721,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B25" t="n">
@@ -1872,7 +1735,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B26" t="n">
@@ -1886,7 +1749,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B27" t="n">
@@ -1940,7 +1803,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B2" t="n">
@@ -1954,7 +1817,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B3" t="n">
@@ -1968,7 +1831,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B4" t="n">
@@ -1982,7 +1845,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B5" t="n">
@@ -1996,7 +1859,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">
@@ -2010,7 +1873,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B7" t="n">
@@ -2024,7 +1887,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B8" t="n">
@@ -2038,7 +1901,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B9" t="n">
@@ -2052,7 +1915,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B10" t="n">
@@ -2066,7 +1929,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B11" t="n">

--- a/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
+++ b/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Leviathan by destinatio" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Exports" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leviathan" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tamar" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Karish YTD" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Leviathan by destinatio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chart - Exports" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Quarterly" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Leviathan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Tamar" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Karish YTD" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Reports" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,8 +26,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -67,13 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -151,13 +150,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -183,22 +182,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$11</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$11</f>
+              <f>'Chart'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -211,22 +210,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$11</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$11</f>
+              <f>'Chart'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -239,22 +238,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$11</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$11</f>
+              <f>'Chart'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -275,8 +274,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -302,8 +301,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -320,7 +319,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -334,7 +333,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -343,13 +342,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -375,10 +374,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -403,10 +402,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -431,10 +430,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -467,8 +466,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -494,8 +493,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -512,7 +511,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -526,7 +525,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -535,13 +534,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -567,22 +566,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Exports'!$A$2:$A$11</f>
+              <f>'Chart - Exports'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports'!$B$2:$B$11</f>
+              <f>'Chart - Exports'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -595,22 +594,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Exports'!$A$2:$A$11</f>
+              <f>'Chart - Exports'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports'!$C$2:$C$11</f>
+              <f>'Chart - Exports'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -623,22 +622,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Exports'!$A$2:$A$11</f>
+              <f>'Chart - Exports'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports'!$D$2:$D$11</f>
+              <f>'Chart - Exports'!$D$2:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -659,8 +658,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -672,8 +671,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -686,8 +685,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -704,7 +703,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -718,7 +717,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -727,7 +726,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -742,9 +741,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -754,7 +753,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -769,9 +768,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -781,7 +780,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -796,9 +795,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1123,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1137,6 +1137,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1147,10 +1148,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Leviathan from Q1 2020; Tamar from Q1 2024 (the owner's site has no English report with the quarterly table earlier); Karish from the announcements found. The national total is given only for quarters all three fields have. Reported 6-10 weeks after each quarter; the pull runs on 15 Jan/Apr/Jul/Oct.</t>
-        </is>
-      </c>
-    </row>
+          <t>Leviathan from Q1 2020; Tamar from Q1 2016 (Q1 2016 - Q4 2023 backfilled once by ISRAEL_TAMAR_HISTORY.py from Tamar Petroleum's English/Hebrew reports on its site and on TASE MAYA: totals rounded to 0.1 BCM before 2021, quarters published as such or as differences of year-to-date figures; domestic/export split from Q3 2020, none published earlier); Karish from Q4 2022 (first gas). The national total is given only for quarters all three fields have (Q4 2022 on). Reported 6-10 weeks after each quarter; the pull runs on 15 Jan/Apr/Jul/Oct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1165,6 +1167,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -1190,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1219,142 +1222,170 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.098679555555556</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9613446111111111</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2746698888888889</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.970184065934066</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9430189120879121</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4268809890109891</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>45292</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B4" t="n">
         <v>1.008991428571429</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C4" t="n">
         <v>1.024514373626374</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D4" t="n">
         <v>0.4656883516483517</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>45383</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B5" t="n">
         <v>1.086606153846154</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" t="n">
         <v>0.8770463956043956</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>0.5044957142857144</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
+    <row r="6">
+      <c r="A6" s="3" t="n">
         <v>45474</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="n">
         <v>1.189951847826087</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C6" t="n">
         <v>1.044086782608696</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
         <v>0.6525542391304348</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>45566</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B7" t="n">
         <v>1.036409673913044</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C7" t="n">
         <v>0.9481229239130435</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" t="n">
         <v>0.4990120652173914</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>45658</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B8" t="n">
         <v>1.137918111111111</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>1.0241263</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D8" t="n">
         <v>0.4669388111111111</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>45748</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B9" t="n">
         <v>0.7761472527472528</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>1.005110692307692</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D9" t="n">
         <v>0.4268809890109891</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>45839</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B10" t="n">
         <v>1.189951847826087</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C10" t="n">
         <v>1.036409673913044</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>0.6563927934782608</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>45931</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>1.074795217391304</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>0.8252891847826086</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.614168695652174</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B12" t="n">
         <v>0.7455325555555556</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C12" t="n">
         <v>1.082984133333333</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D12" t="n">
         <v>0.3766901333333333</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B13" t="n">
         <v>1.047798791208791</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C13" t="n">
         <v>1.051679527472527</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>0.4540461428571428</v>
       </c>
     </row>
@@ -1399,7 +1430,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B2" t="n">
@@ -1413,7 +1444,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B3" t="n">
@@ -1427,7 +1458,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B4" t="n">
@@ -1441,7 +1472,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B5" t="n">
@@ -1455,7 +1486,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B6" t="n">
@@ -1469,7 +1500,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B7" t="n">
@@ -1483,7 +1514,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1497,7 +1528,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -1511,7 +1542,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B10" t="n">
@@ -1525,7 +1556,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B11" t="n">
@@ -1539,7 +1570,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B12" t="n">
@@ -1553,7 +1584,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B13" t="n">
@@ -1567,7 +1598,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B14" t="n">
@@ -1581,7 +1612,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B15" t="n">
@@ -1595,7 +1626,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B16" t="n">
@@ -1609,7 +1640,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B17" t="n">
@@ -1623,7 +1654,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B18" t="n">
@@ -1637,7 +1668,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B19" t="n">
@@ -1651,7 +1682,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B20" t="n">
@@ -1665,7 +1696,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B21" t="n">
@@ -1679,7 +1710,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B22" t="n">
@@ -1693,7 +1724,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B23" t="n">
@@ -1707,7 +1738,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1752,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B25" t="n">
@@ -1735,7 +1766,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B26" t="n">
@@ -1749,7 +1780,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B27" t="n">
@@ -1774,7 +1805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1803,142 +1834,338 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
+        <v>44013</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.2686988043478261</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1919277173913043</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.07677108695652175</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.307084347826087</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2303132608695652</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.06909397826086958</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3139084444444445</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2746698888888889</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09417253333333334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3104589010989012</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2328441758241758</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1008991428571429</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3454698913043479</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.307084347826087</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.07677108695652175</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.3454698913043479</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2303132608695652</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.09596385869565217</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.4316241111111112</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2746698888888889</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1098679555555556</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5433030769230769</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2328441758241758</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1862753406593407</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4222409782608696</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2686988043478261</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.07293253260869566</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4990120652173914</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2686988043478261</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2303132608695652</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5885783333333333</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2746698888888889</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2942891666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.6209178021978023</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2328441758241758</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3104589010989012</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.6525542391304348</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.307084347826087</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1727349456521739</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.5757831521739131</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2303132608695652</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2111204891304348</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>45292</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B16" t="n">
         <v>0.6985325274725276</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C16" t="n">
         <v>0.2328441758241758</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D16" t="n">
         <v>0.3376240549450549</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>45383</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B17" t="n">
         <v>0.6985325274725276</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C17" t="n">
         <v>0.2328441758241758</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D17" t="n">
         <v>0.3026974285714286</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>45474</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B18" t="n">
         <v>0.6909397826086957</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C18" t="n">
         <v>0.307084347826087</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D18" t="n">
         <v>0.2763759130434783</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>45566</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B19" t="n">
         <v>0.614168695652174</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C19" t="n">
         <v>0.2686988043478261</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D19" t="n">
         <v>0.3992096521739131</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
+    <row r="20">
+      <c r="A20" s="3" t="n">
         <v>45658</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B20" t="n">
         <v>0.6670554444444444</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C20" t="n">
         <v>0.3139084444444445</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D20" t="n">
         <v>0.3688424222222222</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>45748</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B21" t="n">
         <v>0.5044957142857144</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C21" t="n">
         <v>0.1940368131868132</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D21" t="n">
         <v>0.3453855274725275</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>45839</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B22" t="n">
         <v>0.6909397826086957</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C22" t="n">
         <v>0.307084347826087</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D22" t="n">
         <v>0.2264747065217391</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
+    <row r="23">
+      <c r="A23" s="3" t="n">
         <v>45931</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B23" t="n">
         <v>0.5373976086956521</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C23" t="n">
         <v>0.307084347826087</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D23" t="n">
         <v>0.3262771195652174</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
+    <row r="24">
+      <c r="A24" s="3" t="n">
         <v>46023</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B24" t="n">
         <v>0.4316241111111112</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C24" t="n">
         <v>0.2354313333333333</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D24" t="n">
         <v>0.2707460333333333</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
+    <row r="25">
+      <c r="A25" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B25" t="n">
         <v>0.6597251648351649</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C25" t="n">
         <v>0.2716515384615384</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D25" t="n">
         <v>0.3880736263736264</v>
       </c>
     </row>
@@ -1954,7 +2181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2031,773 +2258,1141 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>43831</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.621</v>
+        <v>42370</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.854</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.582</v>
+        <v>42461</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.893</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.883</v>
+        <v>42552</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.729</v>
+        <v>42644</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.059</v>
+        <v>42736</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.087</v>
+        <v>42826</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.931</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.075</v>
+        <v>42917</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.921</v>
+        <v>43009</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.883</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.059</v>
+        <v>43101</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.087</v>
+        <v>43191</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.152</v>
+        <v>43282</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.075</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.113</v>
+        <v>43374</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.099</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.275</v>
+        <v>43466</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.427</v>
+        <v>43556</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.931</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.113</v>
+        <v>43647</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.075</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.075</v>
+        <v>43739</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>45292</v>
+        <v>43831</v>
       </c>
       <c r="B18" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D18" t="n">
         <v>0.6</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="F18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6.44</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1.009</v>
+        <v>0.621</v>
       </c>
       <c r="L18" t="n">
-        <v>1.025</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.499</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>45383</v>
+        <v>43922</v>
       </c>
       <c r="B19" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6.359999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="K19" t="n">
-        <v>1.087</v>
+        <v>0.582</v>
       </c>
       <c r="L19" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.468</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>45474</v>
+        <v>44013</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="C20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.5</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.8</v>
-      </c>
       <c r="E20" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="F20" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>7.52</v>
+        <v>0.2</v>
       </c>
       <c r="K20" t="n">
-        <v>1.19</v>
+        <v>0.883</v>
       </c>
       <c r="L20" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.887</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>45566</v>
+        <v>44105</v>
       </c>
       <c r="B21" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="F21" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="G21" t="n">
-        <v>1.43</v>
+        <v>2.27</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>6.47</v>
+        <v>0.18</v>
       </c>
       <c r="K21" t="n">
-        <v>1.036</v>
+        <v>0.729</v>
       </c>
       <c r="L21" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.484</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>45658</v>
+        <v>44197</v>
       </c>
       <c r="B22" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="D22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.8</v>
       </c>
-      <c r="E22" t="n">
-        <v>1.7</v>
-      </c>
       <c r="F22" t="n">
-        <v>2.61</v>
+        <v>1.73</v>
       </c>
       <c r="G22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="J22" t="n">
-        <v>6.699999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="K22" t="n">
-        <v>1.138</v>
+        <v>1.059</v>
       </c>
       <c r="L22" t="n">
-        <v>1.024</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.629</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>45748</v>
+        <v>44287</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="F23" t="n">
-        <v>2.59</v>
+        <v>1.66</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="H23" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>5.69</v>
+        <v>0.26</v>
       </c>
       <c r="K23" t="n">
-        <v>0.776</v>
+        <v>1.087</v>
       </c>
       <c r="L23" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.208</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>45839</v>
+        <v>44378</v>
       </c>
       <c r="B24" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D24" t="n">
         <v>0.8</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="G24" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="H24" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="J24" t="n">
-        <v>7.510000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="K24" t="n">
-        <v>1.19</v>
+        <v>1.075</v>
       </c>
       <c r="L24" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.883</v>
+        <v>1.059</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>45931</v>
+        <v>44470</v>
       </c>
       <c r="B25" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="C25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D25" t="n">
         <v>0.6</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.8</v>
-      </c>
       <c r="E25" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="G25" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="H25" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>6.549999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="K25" t="n">
-        <v>1.075</v>
+        <v>0.921</v>
       </c>
       <c r="L25" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.514</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46023</v>
+        <v>44562</v>
       </c>
       <c r="B26" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E26" t="n">
         <v>1.1</v>
       </c>
       <c r="F26" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="G26" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5.62</v>
+        <v>0.28</v>
       </c>
       <c r="K26" t="n">
-        <v>0.746</v>
+        <v>1.059</v>
       </c>
       <c r="L26" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.205</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.009</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.044</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.891</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.335</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.029999999999999</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.033</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.595</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.499</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6.359999999999999</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.468</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.887</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.484</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J38" t="n">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.629</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.208</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7.510000000000001</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.883</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6.549999999999999</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.514</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.205</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B43" t="n">
         <v>2.7</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C43" t="n">
         <v>0.3</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D43" t="n">
         <v>0.7</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E43" t="n">
         <v>1.7</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F43" t="n">
         <v>2.71</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G43" t="n">
         <v>1.71</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H43" t="n">
         <v>1</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I43" t="n">
         <v>1.17</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J43" t="n">
         <v>6.58</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K43" t="n">
         <v>1.048</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L43" t="n">
         <v>1.052</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M43" t="n">
         <v>0.454</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N43" t="n">
         <v>2.554</v>
       </c>
     </row>
@@ -3430,7 +4025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3462,189 +4057,689 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.87</v>
+        <v>42370</v>
       </c>
       <c r="D2" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Tamar-Financial-Report-q2-2017-Eng.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Tamar-Financial-Report-q2-2017-Eng.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.78</v>
+        <v>42461</v>
       </c>
       <c r="D3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Tamar-Financial-Report-q2-2017-Eng.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.72</v>
+        <v>42552</v>
       </c>
       <c r="D4" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/2017_Delek_Q3_En.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.04</v>
+        <v>42644</v>
       </c>
       <c r="D5" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Annual_Report_2017.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/2017_Delek_Q3_En.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9399999999999999</v>
+        <v>42736</v>
       </c>
       <c r="D6" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/09/Tamar-Petroleum-FS-Q2_2026.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Tamar-Financial-Report-q1-2018.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.89</v>
+        <v>42826</v>
       </c>
       <c r="D7" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/09/Tamar-Petroleum-FS-Q2_2026.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Financial_Statements_Q2_2018.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.59</v>
+        <v>42917</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Financial_Statements_Q3_2018.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.85</v>
+        <v>43009</v>
       </c>
       <c r="D9" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Annual_Report_2018.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Financial_Statements_Q3_2018.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.6899999999999999</v>
+        <v>43101</v>
       </c>
       <c r="D10" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/09/Tamar-Petroleum-FS-Q2_2026.pdf</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Quarterly_Report_Q1_-_2019.pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
+        <v>43191</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Interim_Report_Q2_-_2019.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>43282</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Interim_Report_Q3_-_2019.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>43374</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/08/Annual_Report_2019.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Interim_Report_Q3_-_2019.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>43466</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/09/Interim_Report_Q1_-_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>43556</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/11/Interim_Report_Q2_-_2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>43647</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/11/דוח-רבעון-3-לשנת-2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>43739</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2021/06/Annual_Report_2020.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2020/11/דוח-רבעון-3-לשנת-2020.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2021/05/דוח-רבעון-1-לשנת-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>43922</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2021/08/דוח-רבעון-2-חצי-שנתי-לשנת-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>44013</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>total: https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf | domestic: https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2021/08/דוח-רבעון-2-חצי-שנתי-לשנת-2021.pdf | export: https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2021/08/דוח-רבעון-2-חצי-שנתי-לשנת-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2022/10/Tamar_Petroleum_Ltd_2021.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>total: https://mayafiles.tase.co.il/rpdf/1471001-1472000/P1471381-00.pdf minus https://mayafiles.tase.co.il/rpdf/1471001-1472000/P1471381-00.pdf | domestic: https://mayafiles.tase.co.il/rpdf/1452001-1453000/P1452131-00.pdf | export: https://mayafiles.tase.co.il/rpdf/1452001-1453000/P1452131-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>total: https://mayafiles.tase.co.il/rpdf/1471001-1472000/P1471381-00.pdf | domestic: https://www.tamarpetroleum.co.il/wp-content/uploads/2021/08/דוח-רבעון-2-חצי-שנתי-לשנת-2021.pdf minus https://mayafiles.tase.co.il/rpdf/1452001-1453000/P1452131-00.pdf | export: https://www.tamarpetroleum.co.il/wp-content/uploads/2021/08/דוח-רבעון-2-חצי-שנתי-לשנת-2021.pdf minus https://mayafiles.tase.co.il/rpdf/1452001-1453000/P1452131-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>total: https://mayafiles.tase.co.il/rpdf/1487001-1488000/P1487746-00.pdf | domestic: https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2021/08/דוח-רבעון-2-חצי-שנתי-לשנת-2021.pdf | export: https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2021/08/דוח-רבעון-2-חצי-שנתי-לשנת-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>total: https://www.tamarpetroleum.co.il/wp-content/uploads/2022/10/Tamar_Petroleum_Ltd_2021.pdf minus https://mayafiles.tase.co.il/rpdf/1487001-1488000/P1487746-00.pdf | domestic: https://www.tamarpetroleum.co.il/wp-content/uploads/2022/10/Tamar_Petroleum_Ltd_2021.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf | export: https://www.tamarpetroleum.co.il/wp-content/uploads/2022/10/Tamar_Petroleum_Ltd_2021.pdf minus https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://mayafiles.tase.co.il/rpdf/1559001-1560000/P1559274-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://mayafiles.tase.co.il/rpdf/1559001-1560000/P1559274-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://mayafiles.tase.co.il/rpdf/1559001-1560000/P1559274-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>total: https://mayafiles.tase.co.il/rpdf/1652001-1653000/P1652267-00.pdf minus https://mayafiles.tase.co.il/rpdf/1559001-1560000/P1559274-00.pdf | domestic: https://mayafiles.tase.co.il/rpdf/1652001-1653000/P1652267-00.pdf minus https://mayafiles.tase.co.il/rpdf/1487001-1488000/P1487746-00.pdf | export: https://mayafiles.tase.co.il/rpdf/1652001-1653000/P1652267-00.pdf minus https://mayafiles.tase.co.il/rpdf/1487001-1488000/P1487746-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://mayafiles.tase.co.il/rpdf/1652001-1653000/P1652267-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://mayafiles.tase.co.il/rpdf/1652001-1653000/P1652267-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://mayafiles.tase.co.il/rpdf/1652001-1653000/P1652267-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://mayafiles.tase.co.il/rpdf/1652001-1653000/P1652267-00.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/09/Tamar-Petroleum-FS-Q2_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/09/Tamar-Petroleum-FS-Q2_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/03/Tamar-Petroleum-Financial-Information-2025-Final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/09/Tamar-Petroleum-FS-Q2_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B43" t="n">
         <v>1.71</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C43" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D43" t="n">
         <v>2.71</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2026/09/Tamar-Petroleum-FS-Q2_2026.pdf</t>
         </is>
@@ -3978,7 +5073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4606,217 +5701,217 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/1q-2026-interim-dividend-declaration/9576704</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Tamar-Financial-Report-q2-2017-Eng.pdf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2018-full-year-results-unaudited-/5694564</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/2017_Delek_Q3_En.pdf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2019-full-year-results/6032622</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Annual_Report_2017.pdf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2020-full-year-results/6532513</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Tamar-Financial-Report-q1-2018.pdf</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2021-full-year-results/7049939</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Financial_Statements_Q2_2018.pdf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2022-full-year-results/7278388</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Financial_Statements_Q3_2018.pdf</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2023-full-year-results/8098916</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Annual_Report_2018.pdf</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2024-full-year-results/8788032</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Quarterly_Report_Q1_-_2019.pdf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2025-full-year-results/9481429</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Interim_Report_Q2_-_2019.pdf</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2q-2026-interim-dividend-declaration/9761856</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/07/Interim_Report_Q3_-_2019.pdf</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/08/Annual_Report_2019.pdf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -4826,327 +5921,327 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/agm-results/6088596</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/09/Interim_Report_Q1_-_2020.pdf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/5647922</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/11/Interim_Report_Q2_-_2020.pdf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/6160932</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2020/11/דוח-רבעון-3-לשנת-2020.pdf</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/6764799</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2021/06/Annual_Report_2020.pdf</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/7005741</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2021/05/דוח-רבעון-1-לשנת-2021.pdf</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/7139296</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2021/08/דוח-רבעון-2-חצי-שנתי-לשנת-2021.pdf</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2021-accounts/7049925</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2021/11/דוח-רבעון-3-לשנת-2021.pdf</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2022-accounts/7280046</t>
+          <t>https://www.tamarpetroleum.co.il/wp-content/uploads/2022/10/Tamar_Petroleum_Ltd_2021.pdf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2023-accounts/8099063</t>
+          <t>https://mayafiles.tase.co.il/rpdf/1452001-1453000/P1452131-00.pdf</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2024-accounts/8788235</t>
+          <t>https://mayafiles.tase.co.il/rpdf/1471001-1472000/P1471381-00.pdf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2025-accounts/9481565</t>
+          <t>https://mayafiles.tase.co.il/rpdf/1487001-1488000/P1487746-00.pdf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2021-accounts/6716441</t>
+          <t>https://mayafiles.tase.co.il/rpdf/1523001-1524000/P1523849-00.pdf</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2022-accounts/7271394</t>
+          <t>https://mayafiles.tase.co.il/rpdf/1542001-1543000/P1542518-00.pdf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2023-accounts/7740545</t>
+          <t>https://mayafiles.tase.co.il/rpdf/1559001-1560000/P1559274-00.pdf</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2024-accounts/8410115</t>
+          <t>https://mayafiles.tase.co.il/rpdf/1581001-1582000/P1581015-00.pdf</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2025-accounts/9100696</t>
+          <t>https://mayafiles.tase.co.il/rpdf/1652001-1653000/P1652267-00.pdf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Karish</t>
+          <t>Tamar (history backfill)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2026-accounts/9762113</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/1q-2026-interim-dividend-declaration/9576704</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5156,7 +6251,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -5166,7 +6261,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/half-year-report/6716335</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2018-full-year-results-unaudited-/5694564</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5176,7 +6271,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -5186,7 +6281,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/half-year-results/5236352</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2019-full-year-results/6032622</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5196,7 +6291,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -5206,7 +6301,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/hermes-well-results-and-next-drilling-targets/7248545</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2020-full-year-results/6532513</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5216,7 +6311,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -5226,7 +6321,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/new-gspa-signed-and-karish-operational-update/7140480</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2021-full-year-results/7049939</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5236,7 +6331,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -5246,7 +6341,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/operational-update-karish-project/6273096</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2022-full-year-results/7278388</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5256,7 +6351,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -5266,7 +6361,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/operational-update/6480856</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2023-full-year-results/8098916</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5276,7 +6371,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -5286,7 +6381,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/preliminary-results/5372876</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2024-full-year-results/8788032</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5296,7 +6391,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -5306,7 +6401,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2019/5967502</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2025-full-year-results/9481429</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5316,7 +6411,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -5326,7 +6421,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2020/5940490</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/2q-2026-interim-dividend-declaration/9761856</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5336,7 +6431,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -5346,7 +6441,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2022/7269438</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5356,17 +6451,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2023/7740285</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/agm-results/6088596</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5376,7 +6471,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -5386,7 +6481,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2024/8409918</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/5647922</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5396,17 +6491,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2025/9100543</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/6160932</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5416,17 +6511,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2026/9761841</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/6764799</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5436,17 +6531,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-and-operational-update/5537121</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/7005741</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5456,7 +6551,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -5466,7 +6561,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-and-operational-update/5825003</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/block-listing-interim-review/7139296</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5476,7 +6571,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -5486,7 +6581,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-and-operational-update/5922301</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2021-accounts/7049925</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5496,7 +6591,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -5506,7 +6601,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/5678985</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2022-accounts/7280046</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5516,7 +6611,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -5526,7 +6621,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6040248</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2023-accounts/8099063</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5536,7 +6631,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -5546,7 +6641,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6062395</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2024-accounts/8788235</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5556,7 +6651,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -5566,7 +6661,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6144755</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2025-accounts/9481565</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5576,7 +6671,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -5586,7 +6681,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6657913</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2021-accounts/6716441</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5596,7 +6691,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -5606,7 +6701,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6906259</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2022-accounts/7271394</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5616,7 +6711,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -5626,7 +6721,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7026994</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2023-accounts/7740545</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5636,7 +6731,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -5646,7 +6741,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7412075</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2024-accounts/8410115</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5656,7 +6751,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -5666,7 +6761,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7469608</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2025-accounts/9100696</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5676,17 +6771,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7531891</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-half-year-2026-accounts/9762113</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5696,7 +6791,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -5706,7 +6801,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7884374</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/half-year-report/6716335</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5716,7 +6811,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -5726,7 +6821,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7994777</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/half-year-results/5236352</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5736,7 +6831,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -5746,7 +6841,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/hermes-well-results-and-next-drilling-targets/7248545</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5756,17 +6851,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8577177</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/new-gspa-signed-and-karish-operational-update/7140480</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5776,17 +6871,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8701793</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/operational-update-karish-project/6273096</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5796,17 +6891,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8891249</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/operational-update/6480856</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5816,17 +6911,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9257244</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/preliminary-results/5372876</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5836,17 +6931,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2019/5967502</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5856,30 +6951,570 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-11 15:24</t>
+          <t>2026-10-12 00:12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2020/5940490</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2022/7269438</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2023/7740285</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2024/8409918</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2025/9100543</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2026/9761841</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-and-operational-update/5537121</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-and-operational-update/5825003</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-and-operational-update/5922301</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/5678985</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6040248</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6062395</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6144755</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6657913</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/6906259</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7026994</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7412075</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7469608</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7531891</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7884374</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7994777</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8577177</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8701793</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8891249</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9257244</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Karish</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>Karish</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2026-10-11 15:24</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:12</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
         <v>4</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
+++ b/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
@@ -192,12 +192,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$13</f>
+              <f>'Chart'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$13</f>
+              <f>'Chart'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -220,12 +220,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$13</f>
+              <f>'Chart'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$13</f>
+              <f>'Chart'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -248,12 +248,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$13</f>
+              <f>'Chart'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$13</f>
+              <f>'Chart'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -1148,7 +1148,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Leviathan from Q1 2020; Tamar from Q1 2016 (Q1 2016 - Q4 2023 backfilled once by ISRAEL_TAMAR_HISTORY.py from Tamar Petroleum's English/Hebrew reports on its site and on TASE MAYA: totals rounded to 0.1 BCM before 2021, quarters published as such or as differences of year-to-date figures; domestic/export split from Q3 2020, none published earlier); Karish from Q4 2022 (first gas). The national total is given only for quarters all three fields have (Q4 2022 on). Reported 6-10 weeks after each quarter; the pull runs on 15 Jan/Apr/Jul/Oct.</t>
+          <t>Leviathan from Q1 2020; Tamar from Q1 2016 (Q1 2016 - Q4 2023 backfilled once by ISRAEL_TAMAR_HISTORY.py from Tamar Petroleum's English/Hebrew reports on its site and on TASE MAYA: totals rounded to 0.1 BCM before 2021, quarters published as such or as differences of year-to-date figures; domestic/export split from Q3 2020, none published earlier); Karish from Q4 2022 (first gas). The national total is given only for quarters all three fields have (Q1-Q2 2023 and Q1 2024 on: Karish lacks Q4 2022 and Q3-Q4 2023). Reported 6-10 weeks after each quarter; the pull runs on 15 Jan/Apr/Jul/Oct.</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1223,169 +1223,211 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>44927</v>
+        <v>44835</v>
       </c>
       <c r="B2" t="n">
-        <v>1.098679555555556</v>
+        <v>1.113180760869565</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9613446111111111</v>
+        <v>0.8905446086956522</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2746698888888889</v>
+        <v>0.1074795217391305</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>45017</v>
+        <v>44927</v>
       </c>
       <c r="B3" t="n">
-        <v>0.970184065934066</v>
+        <v>1.098679555555556</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9430189120879121</v>
+        <v>0.9613446111111111</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4268809890109891</v>
+        <v>0.2746698888888889</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>45292</v>
+        <v>45017</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008991428571429</v>
+        <v>0.970184065934066</v>
       </c>
       <c r="C4" t="n">
-        <v>1.024514373626374</v>
+        <v>0.9430189120879121</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4656883516483517</v>
+        <v>0.4268809890109891</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>45383</v>
+        <v>45108</v>
       </c>
       <c r="B5" t="n">
-        <v>1.086606153846154</v>
+        <v>1.113180760869565</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8770463956043956</v>
+        <v>1.032571119565217</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5044957142857144</v>
+        <v>0.4990120652173914</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>45474</v>
+        <v>45200</v>
       </c>
       <c r="B6" t="n">
-        <v>1.189951847826087</v>
+        <v>1.074795217391304</v>
       </c>
       <c r="C6" t="n">
-        <v>1.044086782608696</v>
+        <v>0.5949759239130435</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6525542391304348</v>
+        <v>0.4990120652173914</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>45566</v>
+        <v>45292</v>
       </c>
       <c r="B7" t="n">
-        <v>1.036409673913044</v>
+        <v>1.008991428571429</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9481229239130435</v>
+        <v>1.024514373626374</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4990120652173914</v>
+        <v>0.4656883516483517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>45658</v>
+        <v>45383</v>
       </c>
       <c r="B8" t="n">
-        <v>1.137918111111111</v>
+        <v>1.086606153846154</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0241263</v>
+        <v>0.8770463956043956</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4669388111111111</v>
+        <v>0.5044957142857144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>45748</v>
+        <v>45474</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7761472527472528</v>
+        <v>1.189951847826087</v>
       </c>
       <c r="C9" t="n">
-        <v>1.005110692307692</v>
+        <v>1.044086782608696</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4268809890109891</v>
+        <v>0.6525542391304348</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>45839</v>
+        <v>45566</v>
       </c>
       <c r="B10" t="n">
-        <v>1.189951847826087</v>
+        <v>1.036409673913044</v>
       </c>
       <c r="C10" t="n">
-        <v>1.036409673913044</v>
+        <v>0.9481229239130435</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6563927934782608</v>
+        <v>0.4990120652173914</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>45931</v>
+        <v>45658</v>
       </c>
       <c r="B11" t="n">
-        <v>1.074795217391304</v>
+        <v>1.137918111111111</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8252891847826086</v>
+        <v>1.0241263</v>
       </c>
       <c r="D11" t="n">
-        <v>0.614168695652174</v>
+        <v>0.4669388111111111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46023</v>
+        <v>45748</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7455325555555556</v>
+        <v>0.7761472527472528</v>
       </c>
       <c r="C12" t="n">
-        <v>1.082984133333333</v>
+        <v>1.005110692307692</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3766901333333333</v>
+        <v>0.4268809890109891</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.189951847826087</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.036409673913044</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6563927934782608</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.074795217391304</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8252891847826086</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.614168695652174</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.7455325555555556</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.082984133333333</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3766901333333333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B16" t="n">
         <v>1.047798791208791</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C16" t="n">
         <v>1.051679527472527</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D16" t="n">
         <v>0.4540461428571428</v>
       </c>
     </row>
@@ -2797,11 +2839,23 @@
       <c r="H29" t="n">
         <v>0.6</v>
       </c>
+      <c r="I29" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.5</v>
+      </c>
       <c r="K29" t="n">
         <v>1.113</v>
       </c>
       <c r="L29" t="n">
         <v>0.891</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.111</v>
       </c>
     </row>
     <row r="30">
@@ -2917,11 +2971,23 @@
       <c r="H32" t="n">
         <v>0.45</v>
       </c>
+      <c r="I32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6.89</v>
+      </c>
       <c r="K32" t="n">
         <v>1.113</v>
       </c>
       <c r="L32" t="n">
         <v>1.033</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.645</v>
       </c>
     </row>
     <row r="33">
@@ -2949,11 +3015,23 @@
       <c r="H33" t="n">
         <v>0.55</v>
       </c>
+      <c r="I33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5.649999999999999</v>
+      </c>
       <c r="K33" t="n">
         <v>1.075</v>
       </c>
       <c r="L33" t="n">
         <v>0.595</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.169</v>
       </c>
     </row>
     <row r="34">
@@ -4756,7 +4834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4804,20 +4882,17 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2022-accounts/7280046</t>
         </is>
       </c>
     </row>
@@ -4826,17 +4901,17 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2024/8409918</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
         </is>
       </c>
     </row>
@@ -4845,14 +4920,17 @@
         <v>2023</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>70</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8577177</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2024/8409918</t>
         </is>
       </c>
     </row>
@@ -4861,33 +4939,36 @@
         <v>2023</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8701793</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/7884374</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/energean-israel-full-year-2023-accounts/8099063</t>
         </is>
       </c>
     </row>
@@ -4896,17 +4977,17 @@
         <v>2024</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2025/9100543</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/8215919</t>
         </is>
       </c>
     </row>
@@ -4915,17 +4996,17 @@
         <v>2024</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D9" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2025/9100543</t>
         </is>
       </c>
     </row>
@@ -4934,36 +5015,36 @@
         <v>2024</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D10" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>1.19</v>
+        <v>5.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
         </is>
       </c>
     </row>
@@ -4972,17 +5053,17 @@
         <v>2025</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>2.29</v>
+        <v>1.19</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2026/9761841</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
         </is>
       </c>
     </row>
@@ -4991,17 +5072,17 @@
         <v>2025</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2.29</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2026/9761841</t>
         </is>
       </c>
     </row>
@@ -5010,36 +5091,36 @@
         <v>2025</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/9-months-2025-production-and-adjusted-ebitdax/9196364</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="D15" t="n">
-        <v>0.96</v>
+        <v>5.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9388069</t>
         </is>
       </c>
     </row>
@@ -5048,15 +5129,34 @@
         <v>2026</v>
       </c>
       <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/energean--enog/trading-statement-operational-update/9576511</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B17" t="n">
         <v>6</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>87</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>2.13</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://www.investegate.co.uk/announcement/rns/energean--enog/results-for-half-year-ended-30-june-2026/9761841</t>
         </is>
@@ -6251,7 +6351,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -6271,7 +6371,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -6291,7 +6391,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -6311,7 +6411,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -6331,7 +6431,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -6351,7 +6451,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -6371,7 +6471,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -6391,7 +6491,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -6411,7 +6511,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -6431,7 +6531,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -6451,7 +6551,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -6471,7 +6571,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -6491,7 +6591,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -6511,7 +6611,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -6531,7 +6631,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -6551,7 +6651,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -6571,7 +6671,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -6591,7 +6691,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -6611,11 +6711,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -6631,11 +6731,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -6651,7 +6751,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -6671,7 +6771,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -6691,7 +6791,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -6711,7 +6811,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -6731,11 +6831,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -6751,11 +6851,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -6771,7 +6871,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -6791,11 +6891,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -6811,7 +6911,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -6831,7 +6931,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -6851,7 +6951,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -6871,7 +6971,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -6891,7 +6991,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -6911,7 +7011,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -6931,7 +7031,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -6951,7 +7051,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -6971,7 +7071,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -6991,7 +7091,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -7011,7 +7111,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -7031,7 +7131,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -7051,7 +7151,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -7071,7 +7171,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -7091,7 +7191,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -7111,7 +7211,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -7131,7 +7231,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -7151,7 +7251,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -7171,7 +7271,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -7191,7 +7291,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -7211,7 +7311,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -7231,7 +7331,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -7251,7 +7351,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -7271,7 +7371,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -7291,7 +7391,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -7311,7 +7411,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -7331,11 +7431,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -7351,11 +7451,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -7371,7 +7471,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -7391,7 +7491,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -7411,7 +7511,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -7431,7 +7531,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -7451,7 +7551,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -7471,7 +7571,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -7491,7 +7591,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -7511,7 +7611,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-12 00:12</t>
+          <t>2026-10-12 00:36</t>
         </is>
       </c>
       <c r="D122" t="n">

--- a/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
+++ b/output/Data and Chart Outputs/israel_gas_fields_quarterly.xlsx
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-12 01:00</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="D122" t="n">
